--- a/BDCLIENTES.xlsx
+++ b/BDCLIENTES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\PROGRAMACAO2\AUTOMACAO V1.3 0209\autozap\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ideil\Documents\autozap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B37A97-A133-4365-97A6-86A84C82FE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E305EEE7-700D-41AD-9AA5-30BBF6BA5F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="27">
   <si>
     <t>PESSOA</t>
   </si>
@@ -39,7 +39,73 @@
     <t>ARQUIVO</t>
   </si>
   <si>
+    <t>André</t>
+  </si>
+  <si>
+    <t>Feliz Natal! É que a Familia MJK Distribuidora deseja a você e sua Familía.</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>Rom</t>
+  </si>
+  <si>
+    <t>Irmão Sérgio</t>
+  </si>
+  <si>
+    <t>Júnior</t>
+  </si>
+  <si>
+    <t>Rian</t>
+  </si>
+  <si>
+    <t>Alberto</t>
+  </si>
+  <si>
+    <t>Charles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dan </t>
+  </si>
+  <si>
+    <t>Eric</t>
+  </si>
+  <si>
+    <t>Fabricio</t>
+  </si>
+  <si>
+    <t>Nando</t>
+  </si>
+  <si>
+    <t>Gera boy</t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>Matheus</t>
+  </si>
+  <si>
+    <t>Elivelton</t>
+  </si>
+  <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>+55 75 99193095</t>
+  </si>
+  <si>
+    <t>mjk.jpg</t>
   </si>
 </sst>
 </file>
@@ -89,14 +155,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -377,15 +442,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -399,42 +464,285 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="1" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/BDCLIENTES.xlsx
+++ b/BDCLIENTES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ideil\Documents\autozap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E305EEE7-700D-41AD-9AA5-30BBF6BA5F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937FA7D5-6486-4172-AD15-961F763BB9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="76">
   <si>
     <t>PESSOA</t>
   </si>
@@ -39,9 +39,6 @@
     <t>ARQUIVO</t>
   </si>
   <si>
-    <t>André</t>
-  </si>
-  <si>
     <t>Feliz Natal! É que a Familia MJK Distribuidora deseja a você e sua Familía.</t>
   </si>
   <si>
@@ -57,9 +54,6 @@
     <t>Rom</t>
   </si>
   <si>
-    <t>Irmão Sérgio</t>
-  </si>
-  <si>
     <t>Júnior</t>
   </si>
   <si>
@@ -72,9 +66,6 @@
     <t>Charles</t>
   </si>
   <si>
-    <t xml:space="preserve">Dan </t>
-  </si>
-  <si>
     <t>Eric</t>
   </si>
   <si>
@@ -84,9 +75,6 @@
     <t>Nando</t>
   </si>
   <si>
-    <t>Gera boy</t>
-  </si>
-  <si>
     <t>Lucas</t>
   </si>
   <si>
@@ -102,17 +90,176 @@
     <t>N</t>
   </si>
   <si>
-    <t>+55 75 99193095</t>
-  </si>
-  <si>
     <t>mjk.jpg</t>
+  </si>
+  <si>
+    <t>+55 75 9945-9005</t>
+  </si>
+  <si>
+    <t>+55 75 9152-8890</t>
+  </si>
+  <si>
+    <t>+55 75 9913-8281</t>
+  </si>
+  <si>
+    <t>+55 75 9700-9519</t>
+  </si>
+  <si>
+    <t>+55 75 9828-9980</t>
+  </si>
+  <si>
+    <t>+55 75 9107-7623</t>
+  </si>
+  <si>
+    <t>+55 75 9808-0971</t>
+  </si>
+  <si>
+    <t>+55 75 9928-4957</t>
+  </si>
+  <si>
+    <t>+55 75 9175-2999</t>
+  </si>
+  <si>
+    <t>Paz irmão Sergio</t>
+  </si>
+  <si>
+    <t>+55 75 9290-7317</t>
+  </si>
+  <si>
+    <t>+55 75 9124-1429</t>
+  </si>
+  <si>
+    <t>+55 75 9134-6927</t>
+  </si>
+  <si>
+    <t>Paz irmão Edyerisson</t>
+  </si>
+  <si>
+    <t>+55 71 9183-3311</t>
+  </si>
+  <si>
+    <t>+55 75 9999-5672</t>
+  </si>
+  <si>
+    <t>Cesar</t>
+  </si>
+  <si>
+    <t>+55 75 9215-4737</t>
+  </si>
+  <si>
+    <t>+55 75 9185-4565</t>
+  </si>
+  <si>
+    <t>Dan</t>
+  </si>
+  <si>
+    <t>+55 75 9212-7519</t>
+  </si>
+  <si>
+    <t>Dione</t>
+  </si>
+  <si>
+    <t>+55 19 99383-0481</t>
+  </si>
+  <si>
+    <t>Elton</t>
+  </si>
+  <si>
+    <t>+55 75 9143-2636</t>
+  </si>
+  <si>
+    <t>Genivaldo</t>
+  </si>
+  <si>
+    <t>+55 75 9200-5494</t>
+  </si>
+  <si>
+    <t>Gerson</t>
+  </si>
+  <si>
+    <t>+55 75 9221-3719</t>
+  </si>
+  <si>
+    <t>Hebert</t>
+  </si>
+  <si>
+    <t>+55 75 9814-8552</t>
+  </si>
+  <si>
+    <t>Jonas</t>
+  </si>
+  <si>
+    <t>+55 75 9838-9833</t>
+  </si>
+  <si>
+    <t>Jorge</t>
+  </si>
+  <si>
+    <t>+55 75 8306-9916</t>
+  </si>
+  <si>
+    <t>Leonardo</t>
+  </si>
+  <si>
+    <t>+55 11 98514-5367</t>
+  </si>
+  <si>
+    <t>+55 75 9884-3856</t>
+  </si>
+  <si>
+    <t>Márcio</t>
+  </si>
+  <si>
+    <t>+55 75 9277-7446</t>
+  </si>
+  <si>
+    <t>+55 75 9160-7496</t>
+  </si>
+  <si>
+    <t>Orlando</t>
+  </si>
+  <si>
+    <t>+55 77 9813-9712</t>
+  </si>
+  <si>
+    <t>+55 75 9132-9363</t>
+  </si>
+  <si>
+    <t>Rai</t>
+  </si>
+  <si>
+    <t>+55 11 97726-1410</t>
+  </si>
+  <si>
+    <t>+55 75 9159-5965</t>
+  </si>
+  <si>
+    <t>Gera Boy</t>
+  </si>
+  <si>
+    <t>+55 75 9943-3697</t>
+  </si>
+  <si>
+    <t>+55 75 9239-7030</t>
+  </si>
+  <si>
+    <t>+55 75 9906-1771</t>
+  </si>
+  <si>
+    <t>+55 75 9952-9468</t>
+  </si>
+  <si>
+    <t>Paz irmão Flexon</t>
+  </si>
+  <si>
+    <t>Fala André!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,14 +269,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -155,13 +294,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -466,282 +604,506 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
+      <c r="A4" t="s">
+        <v>75</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
